--- a/projects/multi-state-pharmacy-compliance-database.xlsx
+++ b/projects/multi-state-pharmacy-compliance-database.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
+  <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -530,13 +530,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:B32"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="4" customWidth="1" style="13" min="1" max="1"/>
     <col width="100" customWidth="1" style="13" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="19.5" customHeight="1" s="14">
       <c r="B2" s="15" t="inlineStr">
         <is>
@@ -544,6 +545,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="14">
       <c r="B4" s="16" t="inlineStr">
         <is>
@@ -558,6 +560,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="15" customHeight="1" s="14">
       <c r="B7" s="18" t="inlineStr">
         <is>
@@ -572,6 +575,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="14">
       <c r="B10" s="16" t="inlineStr">
         <is>
@@ -649,6 +653,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="14">
       <c r="B22" s="16" t="inlineStr">
         <is>
@@ -684,12 +689,14 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="14">
       <c r="B28" s="16" t="n"/>
     </row>
     <row r="29" ht="54.75" customHeight="1" s="14">
       <c r="B29" s="17" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31" ht="15" customHeight="1" s="14">
       <c r="B31" s="19" t="inlineStr">
         <is>
@@ -705,6 +712,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4017,6 +4025,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
